--- a/src/test/resources/LoginData.xlsx
+++ b/src/test/resources/LoginData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d38ea065fc9b5a3/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC1048CDE15B65D85ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3AFC068-0639-4713-8C71-1B045574BF62}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048CDE15B65D85ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A615694-53D6-4733-853A-9D6E87BB5EFD}"/>
   <bookViews>
-    <workbookView xWindow="11148" yWindow="180" windowWidth="11844" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>UserName</t>
   </si>
@@ -42,16 +42,10 @@
     <t>sami</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>FAIL</t>
   </si>
   <si>
     <t>Reza</t>
-  </si>
-  <si>
-    <t>Valid</t>
   </si>
   <si>
     <t>Empty</t>
@@ -390,12 +384,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -414,85 +408,74 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>123</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
+      <c r="B6">
+        <v>123</v>
+      </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>123</v>
-      </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
